--- a/VerveStacks_JPN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40DE5B1E-6B00-413C-BFB8-2691D63F6734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10EFEE8-3124-45C1-821F-928B76A07B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4880,7 +4880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F512DE-670C-445D-AF49-DE4D101AB356}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D1F449-1A01-4863-BCE2-FAD8C0959309}">
   <dimension ref="B3:I191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10EFEE8-3124-45C1-821F-928B76A07B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B232AC-8C9B-406D-92B7-D13289C0CF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4880,7 +4880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D1F449-1A01-4863-BCE2-FAD8C0959309}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F0BB8AC-DE25-45CE-97EA-E1AFF7416CC1}">
   <dimension ref="B3:I191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B232AC-8C9B-406D-92B7-D13289C0CF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41D4704-6BAE-40DE-B033-DEDA7A526FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4880,7 +4880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F0BB8AC-DE25-45CE-97EA-E1AFF7416CC1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9A0C0C8-E291-44EB-B201-03C4CB909012}">
   <dimension ref="B3:I191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41D4704-6BAE-40DE-B033-DEDA7A526FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7C7569-058A-41D3-919D-3A9482C4181A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4880,7 +4880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9A0C0C8-E291-44EB-B201-03C4CB909012}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{413ABB37-E33A-4A62-AFA9-B8C5B8E4D60B}">
   <dimension ref="B3:I191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7C7569-058A-41D3-919D-3A9482C4181A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF4AFFD-D82E-4CBA-8B27-D68E35FABAFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4880,7 +4880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{413ABB37-E33A-4A62-AFA9-B8C5B8E4D60B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A72E67-1488-490F-B5A5-688A59194DD8}">
   <dimension ref="B3:I191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF4AFFD-D82E-4CBA-8B27-D68E35FABAFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8769C682-F5CF-4316-B9E4-3DE11DE0CE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4880,7 +4880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A72E67-1488-490F-B5A5-688A59194DD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1509074-D396-497A-B840-E8938E7FF3AF}">
   <dimension ref="B3:I191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8769C682-F5CF-4316-B9E4-3DE11DE0CE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7B939E-D411-4AD0-ADDF-F7F43812E38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4880,7 +4880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1509074-D396-497A-B840-E8938E7FF3AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201C3FFB-3FFE-4D03-A223-7FE9A60A41B5}">
   <dimension ref="B3:I191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7B939E-D411-4AD0-ADDF-F7F43812E38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83AF82C-844E-4E4B-9D40-37D9B5FF7C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4880,7 +4880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201C3FFB-3FFE-4D03-A223-7FE9A60A41B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0A13A1-C5A3-4A2F-A474-5540DE2C2A80}">
   <dimension ref="B3:I191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83AF82C-844E-4E4B-9D40-37D9B5FF7C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895E0337-33FF-4D41-A1C7-FF9ED2A669FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4880,7 +4880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0A13A1-C5A3-4A2F-A474-5540DE2C2A80}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0179089D-F26D-401C-B4FF-1787CAB55B1D}">
   <dimension ref="B3:I191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
